--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="666">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -320,16 +320,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -455,7 +455,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -494,7 +494,15 @@
 このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
-    <t>これは業務IDであって、リソースに対するIDではない。</t>
+    <t xml:space="preserve">これは業務IDであって、リソースに対するIDではない。  
+Slice定義は下記のようになる。  
+[Sliceで定義される識別子]  
+　- rpNumber : 処方箋内部の剤グループとしてのRp番号  
+　- orderInRp : 同一RP番号（剤グループ）での薬剤の表記順  
+　- requestIdentifier : 処方オーダに対するID  
+　- prescriptionIdentifierCommon : 全国で⼀意になる発番ルールにもとづき発行される処方箋ID  
+[invariantで定義される識別子]  
+　- jp-inv-local-prescriptionid : 医療機関毎に管理される処方箋に対するID  </t>
   </si>
   <si>
     <t xml:space="preserve">value:system}
@@ -504,6 +512,10 @@
     <t>open</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+jp-inv-local-prescriptionid:施設処方箋IDを記述する場合には、identifier.systemは、'urn:oid:1.2.392.100495.20.3.11.[1+施設番号10桁]'でなければならない。 {system.all(substring(0,31)!='urn:oid:1.2.392.100495.20.3.11.' or substring(31).matches('^1(0[1-9]|[1-3][0-9]|4[0-7])([0-9])([0-9]{7})$'))}</t>
+  </si>
+  <si>
     <t>Request.identifier</t>
   </si>
   <si>
@@ -584,19 +596,19 @@
     <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
   </si>
   <si>
-    <t>この識別子の目的。 / The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>アプリケーションは、識別子が一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -618,22 +630,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -654,16 +666,16 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
-  </si>
-  <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
+  </si>
+  <si>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -712,7 +724,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -737,10 +749,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -785,10 +797,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationRequest.identifier:orderInRp.value</t>
@@ -806,100 +818,100 @@
     <t>MedicationRequest.identifier:orderInRp.assigner</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon</t>
-  </si>
-  <si>
-    <t>requestIdentifierCommon</t>
+    <t>MedicationRequest.identifier:requestIdentifier</t>
+  </si>
+  <si>
+    <t>requestIdentifier</t>
+  </si>
+  <si>
+    <t>処方オーダに対するID</t>
+  </si>
+  <si>
+    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
+  </si>
+  <si>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.system</t>
+  </si>
+  <si>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.value</t>
+  </si>
+  <si>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon</t>
+  </si>
+  <si>
+    <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
     <t>処方箋に対するID</t>
   </si>
   <si>
-    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。system 要素には、保険医療機関番号を含む処方箋ID（urn:oid:1.2.392.100495.20.3.11.1[保険医療機関コード(10 桁)]）を指定する。全国で⼀意になる発番ルールにもとづく場合には urn:oid:1.2.392.100495.20.3.11 とする。</t>
-  </si>
-  <si>
-    <t>これはビジネス識別子であり、リソース識別子ではありません。 / This is a business identifier, not a resource identifier.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.system</t>
-  </si>
-  <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.id</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.extension</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.use</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.type</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.system</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.value</t>
-  </si>
-  <si>
-    <t>一意の値 / The value that is unique</t>
-  </si>
-  <si>
-    <t>通常、識別子の部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifierCommon.assigner</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier</t>
-  </si>
-  <si>
-    <t>requestIdentifier</t>
-  </si>
-  <si>
-    <t>処方オーダに対するID</t>
-  </si>
-  <si>
-    <t>薬剤をオーダする単位としての処方依頼に対するID。MedicationRequestは単一の薬剤でインスタンスが作成される。</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.use</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.type</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.system</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.value</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.period</t>
-  </si>
-  <si>
-    <t>MedicationRequest.identifier:requestIdentifier.assigner</t>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.value</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.period</t>
+  </si>
+  <si>
+    <t>MedicationRequest.identifier:prescriptionIdentifierCommon.assigner</t>
   </si>
   <si>
     <t>MedicationRequest.status</t>
@@ -1514,13 +1526,19 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>薬をどのように服用すべきか / How the medication should be taken</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>薬の要求には、経口投与または静脈内または筋肉内の用量のオプションが含まれる場合があります。たとえば、「吐き気に必要に応じて、1日に2回Ondansetron 8mgまたはIV」または「Compazine®（プロクロロペラジン）5-10mg POまたは25mg PR BID PRN吐き気または嘔吐」。これらの場合、グループ化できる2つの投薬要求が作成されます。使用する投与経路の決定は、用量が必要な時点での患者の状態に基づいています。 / There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
-    <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
+    <t>Request.occurrence[x]</t>
+  </si>
+  <si>
+    <t>see dosageInstruction mapping</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1654,14 +1672,7 @@
     <t>このエレメントはどのような量を表現するか定義するためにコンテキストにあわせてよく定義される。したがって、どのような単位でも利用することができる。使用されるコンテキストによってcomparatorエレメントで値が定義されることもある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>Supply.quantity[moodCode=RQO]</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.initialFill.duration</t>
@@ -1797,6 +1808,15 @@
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
+  </si>
+  <si>
+    <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
@@ -2410,7 +2430,7 @@
   <cols>
     <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="24.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -3723,33 +3743,33 @@
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>82</v>
@@ -3774,13 +3794,13 @@
         <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3845,27 +3865,27 @@
         <v>103</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3888,13 +3908,13 @@
         <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3945,7 +3965,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3966,7 +3986,7 @@
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>82</v>
@@ -3977,10 +3997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4009,7 +4029,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>140</v>
@@ -4050,10 +4070,10 @@
         <v>82</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>82</v>
@@ -4062,7 +4082,7 @@
         <v>155</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -4083,7 +4103,7 @@
         <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>82</v>
@@ -4094,10 +4114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4123,16 +4143,16 @@
         <v>111</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>82</v>
@@ -4157,13 +4177,13 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
@@ -4181,7 +4201,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4202,7 +4222,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -4213,10 +4233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4239,19 +4259,19 @@
         <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>82</v>
@@ -4276,13 +4296,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4300,7 +4320,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -4321,21 +4341,21 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4361,23 +4381,23 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="S17" t="s" s="2">
         <v>82</v>
@@ -4419,7 +4439,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4440,21 +4460,21 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4477,16 +4497,16 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4536,7 +4556,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4557,21 +4577,21 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4594,13 +4614,13 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4651,7 +4671,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4672,21 +4692,21 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4709,16 +4729,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4768,7 +4788,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4789,24 +4809,24 @@
         <v>82</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>82</v>
@@ -4831,13 +4851,13 @@
         <v>150</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4902,27 +4922,27 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4945,13 +4965,13 @@
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5002,7 +5022,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5023,7 +5043,7 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -5034,10 +5054,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5066,7 +5086,7 @@
         <v>138</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>140</v>
@@ -5107,10 +5127,10 @@
         <v>82</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>82</v>
@@ -5119,7 +5139,7 @@
         <v>155</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5140,7 +5160,7 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -5151,10 +5171,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5180,16 +5200,16 @@
         <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5214,13 +5234,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5238,7 +5258,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5259,7 +5279,7 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -5270,10 +5290,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5296,19 +5316,19 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
@@ -5333,13 +5353,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5357,7 +5377,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5378,21 +5398,21 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5418,23 +5438,23 @@
         <v>105</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5476,7 +5496,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5497,21 +5517,21 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5534,16 +5554,16 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5593,7 +5613,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5614,21 +5634,21 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5651,13 +5671,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5708,7 +5728,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5729,21 +5749,21 @@
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5766,16 +5786,16 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5825,7 +5845,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5846,24 +5866,24 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>82</v>
@@ -5873,7 +5893,7 @@
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -5888,13 +5908,13 @@
         <v>150</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5959,27 +5979,27 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6002,13 +6022,13 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6059,7 +6079,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6080,7 +6100,7 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
@@ -6091,10 +6111,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6123,7 +6143,7 @@
         <v>138</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N32" t="s" s="2">
         <v>140</v>
@@ -6164,10 +6184,10 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
@@ -6176,7 +6196,7 @@
         <v>155</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6197,7 +6217,7 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -6208,10 +6228,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6237,16 +6257,16 @@
         <v>111</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6271,13 +6291,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6295,7 +6315,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6316,7 +6336,7 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>82</v>
@@ -6327,10 +6347,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6353,19 +6373,19 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
@@ -6390,13 +6410,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6414,7 +6434,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6435,21 +6455,21 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6475,23 +6495,23 @@
         <v>105</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6533,7 +6553,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6554,21 +6574,21 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6591,16 +6611,16 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6650,7 +6670,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6671,21 +6691,21 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6708,13 +6728,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6765,7 +6785,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6786,21 +6806,21 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6823,16 +6843,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6882,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6903,24 +6923,24 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s" s="2">
         <v>148</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>82</v>
@@ -6930,7 +6950,7 @@
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6945,13 +6965,13 @@
         <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7016,27 +7036,27 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7059,13 +7079,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7116,7 +7136,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7137,7 +7157,7 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>82</v>
@@ -7148,10 +7168,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7180,7 +7200,7 @@
         <v>138</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>140</v>
@@ -7221,10 +7241,10 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
@@ -7233,7 +7253,7 @@
         <v>155</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7254,7 +7274,7 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>82</v>
@@ -7265,10 +7285,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7294,16 +7314,16 @@
         <v>111</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7328,13 +7348,13 @@
         <v>82</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>82</v>
@@ -7352,7 +7372,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7373,7 +7393,7 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>82</v>
@@ -7384,10 +7404,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7410,19 +7430,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7447,13 +7467,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7471,7 +7491,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7492,21 +7512,21 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7532,23 +7552,23 @@
         <v>105</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7590,7 +7610,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7611,21 +7631,21 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7648,16 +7668,16 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7707,7 +7727,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7728,21 +7748,21 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7765,13 +7785,13 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7822,7 +7842,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7843,21 +7863,21 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7880,16 +7900,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7939,7 +7959,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7960,21 +7980,21 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8000,13 +8020,13 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8032,13 +8052,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -8056,7 +8076,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -8071,16 +8091,16 @@
         <v>103</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8088,10 +8108,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8114,16 +8134,16 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8149,13 +8169,13 @@
         <v>82</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>82</v>
@@ -8173,7 +8193,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8188,13 +8208,13 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
@@ -8205,10 +8225,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8234,13 +8254,13 @@
         <v>111</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8266,13 +8286,13 @@
         <v>82</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>82</v>
@@ -8290,7 +8310,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>91</v>
@@ -8305,16 +8325,16 @@
         <v>103</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8322,10 +8342,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8348,16 +8368,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8387,7 +8407,7 @@
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>82</v>
@@ -8405,7 +8425,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8423,13 +8443,13 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8437,10 +8457,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8466,13 +8486,13 @@
         <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8498,13 +8518,13 @@
         <v>82</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>82</v>
@@ -8522,7 +8542,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8537,16 +8557,16 @@
         <v>103</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8554,10 +8574,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8580,16 +8600,16 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8639,7 +8659,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8660,7 +8680,7 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8691,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8697,13 +8717,13 @@
         <v>92</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8754,7 +8774,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8775,7 +8795,7 @@
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>82</v>
@@ -8786,10 +8806,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8812,16 +8832,16 @@
         <v>92</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8850,10 +8870,10 @@
         <v>115</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8871,7 +8891,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>91</v>
@@ -8886,27 +8906,27 @@
         <v>103</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8929,16 +8949,16 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8988,7 +9008,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>91</v>
@@ -9003,27 +9023,27 @@
         <v>103</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9046,16 +9066,16 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9105,7 +9125,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9120,27 +9140,27 @@
         <v>103</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9163,16 +9183,16 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9222,7 +9242,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9237,16 +9257,16 @@
         <v>103</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9254,10 +9274,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9280,13 +9300,13 @@
         <v>92</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9337,7 +9357,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9352,27 +9372,27 @@
         <v>103</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9395,16 +9415,16 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9454,7 +9474,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9469,16 +9489,16 @@
         <v>103</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9486,10 +9506,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9512,16 +9532,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9571,7 +9591,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9586,16 +9606,16 @@
         <v>103</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
@@ -9603,10 +9623,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9629,16 +9649,16 @@
         <v>92</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9664,11 +9684,11 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9686,7 +9706,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9701,13 +9721,13 @@
         <v>103</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>82</v>
@@ -9718,10 +9738,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9744,16 +9764,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9803,7 +9823,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9824,10 +9844,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9835,10 +9855,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9861,16 +9881,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9896,13 +9916,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9920,7 +9940,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9935,27 +9955,27 @@
         <v>103</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,16 +9998,16 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10037,7 +10057,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10052,16 +10072,16 @@
         <v>103</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10069,10 +10089,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10095,16 +10115,16 @@
         <v>92</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10154,7 +10174,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10169,13 +10189,13 @@
         <v>103</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>82</v>
@@ -10186,10 +10206,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10215,13 +10235,13 @@
         <v>105</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10271,7 +10291,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10292,7 +10312,7 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>82</v>
@@ -10303,10 +10323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10329,16 +10349,16 @@
         <v>92</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10388,7 +10408,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10403,13 +10423,13 @@
         <v>103</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>82</v>
@@ -10420,10 +10440,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10449,14 +10469,14 @@
         <v>150</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10505,7 +10525,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10520,13 +10540,13 @@
         <v>103</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>82</v>
@@ -10537,10 +10557,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10563,16 +10583,16 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10598,13 +10618,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10622,7 +10642,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10643,7 +10663,7 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10674,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10680,16 +10700,16 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10739,7 +10759,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10754,13 +10774,13 @@
         <v>103</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>82</v>
@@ -10771,10 +10791,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10797,16 +10817,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10856,7 +10876,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10871,13 +10891,13 @@
         <v>103</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10908,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10914,16 +10934,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10973,7 +10993,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10988,13 +11008,13 @@
         <v>103</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>82</v>
@@ -11005,10 +11025,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11031,13 +11051,13 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11088,7 +11108,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11106,10 +11126,10 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>82</v>
@@ -11120,10 +11140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11146,13 +11166,13 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11203,7 +11223,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11224,7 +11244,7 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>82</v>
@@ -11235,10 +11255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11264,10 +11284,10 @@
         <v>137</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11306,7 +11326,7 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC76" s="2"/>
       <c r="AD76" t="s" s="2">
@@ -11316,7 +11336,7 @@
         <v>155</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11348,13 +11368,13 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>488</v>
-      </c>
       <c r="C77" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -11376,13 +11396,13 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11433,7 +11453,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11442,7 +11462,7 @@
         <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>142</v>
@@ -11465,13 +11485,13 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>82</v>
@@ -11493,13 +11513,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11550,7 +11570,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11559,7 +11579,7 @@
         <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>142</v>
@@ -11582,14 +11602,14 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11611,10 +11631,10 @@
         <v>137</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>140</v>
@@ -11669,7 +11689,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11701,10 +11721,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11727,16 +11747,16 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11786,7 +11806,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11807,7 +11827,7 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>82</v>
@@ -11818,10 +11838,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11844,13 +11864,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11901,7 +11921,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11922,7 +11942,7 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>82</v>
@@ -11933,10 +11953,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11965,7 +11985,7 @@
         <v>138</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>140</v>
@@ -12018,7 +12038,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12039,7 +12059,7 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>82</v>
@@ -12050,14 +12070,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12079,10 +12099,10 @@
         <v>137</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>140</v>
@@ -12137,7 +12157,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12169,10 +12189,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12195,16 +12215,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12254,7 +12274,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12263,10 +12283,10 @@
         <v>91</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>520</v>
+        <v>103</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12275,21 +12295,21 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12312,16 +12332,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12371,7 +12391,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12392,7 +12412,7 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>82</v>
@@ -12403,10 +12423,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12429,16 +12449,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12488,7 +12508,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12509,7 +12529,7 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>82</v>
@@ -12520,10 +12540,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12546,19 +12566,19 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12607,7 +12627,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12625,10 +12645,10 @@
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>82</v>
@@ -12639,10 +12659,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12665,13 +12685,13 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12722,7 +12742,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12743,7 +12763,7 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>82</v>
@@ -12754,10 +12774,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12786,7 +12806,7 @@
         <v>138</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>140</v>
@@ -12827,10 +12847,10 @@
         <v>82</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>82</v>
@@ -12839,7 +12859,7 @@
         <v>155</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12860,7 +12880,7 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>82</v>
@@ -12871,10 +12891,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12897,16 +12917,16 @@
         <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12956,7 +12976,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -12965,7 +12985,7 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>103</v>
@@ -12977,21 +12997,21 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13014,23 +13034,23 @@
         <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q91" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="R91" t="s" s="2">
         <v>82</v>
@@ -13075,7 +13095,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13084,7 +13104,7 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>103</v>
@@ -13096,21 +13116,21 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13133,16 +13153,16 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13192,7 +13212,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13210,24 +13230,24 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13250,16 +13270,16 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13309,7 +13329,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13318,33 +13338,33 @@
         <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>520</v>
+        <v>103</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>522</v>
+        <v>570</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13367,16 +13387,16 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13426,7 +13446,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13444,10 +13464,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13458,10 +13478,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13484,13 +13504,13 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13541,7 +13561,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13562,7 +13582,7 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>82</v>
@@ -13573,10 +13593,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13605,7 +13625,7 @@
         <v>138</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>140</v>
@@ -13646,10 +13666,10 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
@@ -13658,7 +13678,7 @@
         <v>155</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13679,7 +13699,7 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>82</v>
@@ -13690,10 +13710,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13716,19 +13736,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13777,7 +13797,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13798,21 +13818,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13838,20 +13858,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13872,13 +13892,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13896,7 +13916,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13917,21 +13937,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13954,24 +13974,24 @@
         <v>92</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14013,7 +14033,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14034,21 +14054,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14074,21 +14094,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14130,7 +14150,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14139,7 +14159,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14151,21 +14171,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14191,23 +14211,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14249,7 +14269,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14270,21 +14290,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14307,16 +14327,16 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14366,7 +14386,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14387,10 +14407,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14398,10 +14418,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14424,13 +14444,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14481,7 +14501,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14499,10 +14519,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14513,10 +14533,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14539,13 +14559,13 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14596,7 +14616,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14617,7 +14637,7 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>82</v>
@@ -14628,10 +14648,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14660,7 +14680,7 @@
         <v>138</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>140</v>
@@ -14713,7 +14733,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14734,7 +14754,7 @@
         <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>82</v>
@@ -14745,14 +14765,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -14774,10 +14794,10 @@
         <v>137</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>140</v>
@@ -14832,7 +14852,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14864,10 +14884,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14890,16 +14910,16 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14929,7 +14949,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14947,7 +14967,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14965,24 +14985,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15005,16 +15025,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15040,31 +15060,31 @@
         <v>82</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF108" t="s" s="2">
         <v>641</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15082,24 +15102,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15122,16 +15142,16 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -15181,7 +15201,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15196,13 +15216,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15213,14 +15233,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15239,16 +15259,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15298,7 +15318,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15319,7 +15339,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15330,10 +15350,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15356,16 +15376,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15415,7 +15435,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15430,13 +15450,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4149" uniqueCount="671">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -276,7 +276,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -881,7 +881,7 @@
     <t>prescriptionIdentifierCommon</t>
   </si>
   <si>
-    <t>処方箋に対するID</t>
+    <t>全国で⼀意となる処方箋ID</t>
   </si>
   <si>
     <t>薬剤をオーダする単位としての処方箋に対するID。MedicationRequestは単一の薬剤でインスタンスが作成されるが、それの集合としての処方箋のID。全国で⼀意になる発番ルールにもとづき urn:oid:1.2.392.100495.20.3.11 とする。</t>
@@ -1074,8 +1074,8 @@
     <t>MedicationRequest.reported[x]</t>
   </si>
   <si>
-    <t>boolean
-Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Organization)</t>
+    <t xml:space="preserve">Reference(Patient|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Patient|Practitioner|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Practitioner|PractitionerRole|http://jpfhir.jp/fhir/core/StructureDefinition/JP_PractitionerRole|RelatedPerson|Organization|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Organization)
+</t>
   </si>
   <si>
     <t>初期記録にはない報告</t>
@@ -1099,7 +1099,7 @@
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.  
 ひとつのtext要素と、複数のcoding 要素を記述できる。処方オーダ時に選択または入力し、実際に処方箋に印字される文字列を必ずtext要素に格納した上で、それをコード化した情報を1個以上のcoding 要素に記述する。  
-厚生労働省標準であるHOT9コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
+厚生労働省標準であるHOT9、HOT13コード（販社指定が不要な場合にはHOT7コード）または広く流通しているYJコードを用いるか、一般名処方の場合には厚生労働省保険局一般名処方マスタのコードを使用して、Coding要素（コードsystemを識別するURI、医薬品のコード、そのコード表における医薬品の名称の3つからなる）で記述する。  
 なお、上記のいずれの標準的コードも付番されていない医薬品や医療材料の場合には、薬機法の下で使用されているGS1標準の識別コードであるGTIN(Global Trade Item Number)の調剤包装単位（最少包装単位、個別包装単位）14桁を使用する。  
 ひとつの処方薬、医療材料を複数のコード体系のコードで記述してもよく、その場合にcoding 要素を繰り返して記述する。  
 ただし、ひとつの処方薬を複数のコードで繰り返し記述する場合には、それらのコードが指し示す処方薬、医療材料は当然同一でなければならない。  
@@ -1226,7 +1226,7 @@
 </t>
   </si>
   <si>
-    <t>この処方オーダが最初に記述された日</t>
+    <t>この処方オーダが最初に記述された日時</t>
   </si>
   <si>
     <t>JP Coreでは必須。処方指示が最初に作成された日時。秒の精度まで記録する。タイムゾーンも付与しなければならない。</t>
@@ -1420,7 +1420,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|MedicationRequest|ServiceRequest|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(CarePlan|http://jpfhir.jp/fhir/core/StructureDefinition/JP_CarePlan|MedicationRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRequest|ServiceRequest|http://jpfhir.jp/fhir/core/StructureDefinition/JP_ServiceRequest_Common|ImmunizationRecommendation)
 </t>
   </si>
   <si>
@@ -1501,7 +1501,7 @@
 </t>
   </si>
   <si>
-    <t>薬剤単位の備考</t>
+    <t>薬剤オーダごとの備考</t>
   </si>
   <si>
     <t>他の属性では伝えることができなかったMedicationRequestについての付加的情報。</t>
@@ -1804,12 +1804,15 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>調剤量</t>
+    <t>払い出される薬剤量</t>
   </si>
   <si>
     <t>1回の調剤で払い出される薬剤の量</t>
   </si>
   <si>
+    <t>調剤後に払い出されるべき薬剤の量である。1日3錠、7日分という指示であれば21錠が払い出されるべき量である</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/DaysSupply</t>
   </si>
   <si>
@@ -1822,13 +1825,13 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration</t>
   </si>
   <si>
-    <t>調剤日数</t>
-  </si>
-  <si>
-    <t>供給される製品が使用されるか、あるいは払い出しが想定されている時間を指定する期間。</t>
-  </si>
-  <si>
-    <t>状況によっては、この属性は物理的に供給される量というよりも、想定されている期間に供給される薬剤の量を指定する数量の代わりに使われることもある。たとえば、薬剤が90日間供給される（オーダされた量に基づいて）など。可能であれば、量も示した方がより正確になる。expectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
+    <t>払い出される薬剤が想定された使用期間</t>
+  </si>
+  <si>
+    <t>払い出される薬剤が使用されることが想定された期間。</t>
+  </si>
+  <si>
+    <t>状況によっては、薬剤が供給される量として薬剤の錠数などの物理的量よりも、想定される供給期間を使って表現されることもある。たとえば、オーダされた量に基づいて薬剤を90日分提供するなど。可能であれば、量も示した方がより正確になる。ただし、実際には飲み忘れや紛失もあるためexpectedSupplyDurationは外部要因に影響をうけることのある予測値である。</t>
   </si>
   <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
@@ -1874,7 +1877,7 @@
     <t>MedicationRequest.dispenseRequest.expectedSupplyDuration.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -1886,7 +1889,7 @@
     <t>コンパレータがない場合、値の変更はありません / If there is no comparator, then there is no modification of the value</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -13279,7 +13282,7 @@
         <v>567</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>522</v>
+        <v>568</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -13347,24 +13350,24 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13390,13 +13393,13 @@
         <v>525</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13446,7 +13449,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13464,10 +13467,10 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>82</v>
@@ -13478,10 +13481,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,10 +13596,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13710,10 +13713,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13736,19 +13739,19 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13797,7 +13800,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13818,21 +13821,21 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13858,20 +13861,20 @@
         <v>111</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q98" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="R98" t="s" s="2">
         <v>82</v>
@@ -13895,10 +13898,10 @@
         <v>186</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13916,7 +13919,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -13937,21 +13940,21 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13977,21 +13980,21 @@
         <v>169</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q99" s="2"/>
       <c r="R99" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="S99" t="s" s="2">
         <v>82</v>
@@ -14033,7 +14036,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14054,21 +14057,21 @@
         <v>82</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14094,21 +14097,21 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>82</v>
@@ -14150,7 +14153,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14159,7 +14162,7 @@
         <v>91</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>103</v>
@@ -14171,21 +14174,21 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14211,23 +14214,23 @@
         <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>82</v>
@@ -14269,7 +14272,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14290,21 +14293,21 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14327,13 +14330,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>376</v>
@@ -14386,7 +14389,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14407,7 +14410,7 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>413</v>
@@ -14418,10 +14421,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14447,10 +14450,10 @@
         <v>483</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14501,7 +14504,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14519,10 +14522,10 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>82</v>
@@ -14533,10 +14536,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14648,10 +14651,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14765,10 +14768,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14884,10 +14887,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14913,13 +14916,13 @@
         <v>193</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14949,7 +14952,7 @@
       </c>
       <c r="Y107" s="2"/>
       <c r="Z107" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -14967,7 +14970,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>91</v>
@@ -14985,24 +14988,24 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15028,13 +15031,13 @@
         <v>193</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15063,10 +15066,10 @@
         <v>301</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>82</v>
@@ -15084,7 +15087,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15102,24 +15105,24 @@
         <v>82</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15142,13 +15145,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>376</v>
@@ -15201,7 +15204,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15216,13 +15219,13 @@
         <v>103</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>82</v>
@@ -15233,14 +15236,14 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15259,16 +15262,16 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15318,7 +15321,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15339,7 +15342,7 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>82</v>
@@ -15350,10 +15353,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15376,16 +15379,16 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15435,7 +15438,7 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -15450,13 +15453,13 @@
         <v>103</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -2431,17 +2431,17 @@
   <dimension ref="A1:AO111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="69.44921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="28.5078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="24.44140625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="244.94140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2450,27 +2450,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="178.55859375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="75.55078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="59.37890625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="153.08203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.76953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="50.90625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="110.09375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -374,7 +374,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -648,7 +648,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -742,7 +742,7 @@
     <t>MedicationRequest.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -959,7 +959,7 @@
     <t>特定のステータスの理由を特定します。 / Identifies the reasons for a given status.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.statusReason</t>
@@ -1200,7 +1200,7 @@
     <t>MedicationRequest.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1346,7 +1346,7 @@
     <t>薬が注文された理由を示すコード化された概念。 / A coded concept indicating why the medication was ordered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1469,7 +1469,7 @@
     <t>投薬投与の全体的なパターンを特定します。 / Identifies the overall pattern of medication administratio.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationrequest-course-of-therapy|4.0.1</t>
   </si>
   <si>
     <t>Act.code where classCode = LIST and moodCode = EVN</t>
@@ -2066,7 +2066,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -2089,7 +2089,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -2108,7 +2108,7 @@
     <t>MedicationRequest.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-medicationrequest.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
